--- a/asset/data/door_access_log.xlsx
+++ b/asset/data/door_access_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11540"/>
+    <workbookView windowWidth="28800" windowHeight="13060"/>
   </bookViews>
   <sheets>
     <sheet name="door_access_log" sheetId="1" r:id="rId1"/>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1">
-        <v>0.327951388888889</v>
+        <v>0.3328125</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>

--- a/asset/data/door_access_log.xlsx
+++ b/asset/data/door_access_log.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13060"/>
+    <workbookView windowWidth="28800" windowHeight="11540"/>
   </bookViews>
   <sheets>
     <sheet name="door_access_log" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">door_access_log!$C$1:$C$147</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -3178,7 +3181,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="1">
-        <v>0.579953703703704</v>
+        <v>0.583310185185185</v>
       </c>
       <c r="B86" t="s">
         <v>11</v>
